--- a/7RSuperMarketProject/src/main/resources/AdminUserFile.xlsx
+++ b/7RSuperMarketProject/src/main/resources/AdminUserFile.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\git\7RMyproject\7RSuperMarketProject\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0576A27-1B89-4ABA-9DF1-EC74C890D3C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08CB3C0-E064-4DD7-B86B-CD3A71910A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{576494C9-9B19-41CF-97D3-7945EB1D889B}"/>
   </bookViews>
   <sheets>
     <sheet name="AdminUserTest" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t>username</t>
   </si>
@@ -45,6 +46,18 @@
   </si>
   <si>
     <t>admin</t>
+  </si>
+  <si>
+    <t>categoryfield</t>
+  </si>
+  <si>
+    <t>jewellery</t>
+  </si>
+  <si>
+    <t>enternews</t>
+  </si>
+  <si>
+    <t>hello world</t>
   </si>
 </sst>
 </file>
@@ -416,26 +429,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC858802-3A00-4312-9DEF-FD5CACF47967}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{336B2FC1-2948-409F-AD9F-9EF1BA3864B7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/7RSuperMarketProject/src/main/resources/AdminUserFile.xlsx
+++ b/7RSuperMarketProject/src/main/resources/AdminUserFile.xlsx
@@ -3,12 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\git\7RMyproject\7RSuperMarketProject\src\main\resources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08CB3C0-E064-4DD7-B86B-CD3A71910A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{D0713D75-5A63-4A2A-A265-D606F2F97AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{576494C9-9B19-41CF-97D3-7945EB1D889B}"/>
   </bookViews>
@@ -16,7 +11,8 @@
     <sheet name="AdminUserTest" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
